--- a/public/downloads/goldfin-template-vault.xlsx
+++ b/public/downloads/goldfin-template-vault.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="$#,##0;[Red]($#,##0);-"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot; mo&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
   <fonts count="6">
@@ -192,7 +192,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -215,7 +215,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>38400</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="8">
@@ -225,7 +225,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>52300</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="9">
@@ -235,7 +235,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <v>-41180</v>
+        <v>-71900</v>
       </c>
     </row>
     <row r="10">
@@ -245,7 +245,7 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="11">
@@ -369,7 +369,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 to 2026-05-31</t>
+          <t>2026-05-01 to 2026-05-31</t>
         </is>
       </c>
     </row>
@@ -400,7 +400,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>38400</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="7">
@@ -410,7 +410,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>52300</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="8">
@@ -420,7 +420,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>-41180</v>
+        <v>-71900</v>
       </c>
     </row>
     <row r="9">
@@ -430,7 +430,7 @@
         </is>
       </c>
       <c r="B9" s="9">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="10">
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <v>6800</v>
+        <v>72948</v>
       </c>
     </row>
     <row r="11">
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B11" s="11">
-        <v>5.6</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="12">
@@ -550,7 +550,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 to 2026-05-31</t>
+          <t>2026-05-01 to 2026-05-31</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>38400</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>22881.25</v>
+        <v>22493.33</v>
       </c>
     </row>
     <row r="8">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>-18016.25</v>
+        <v>-16776.67</v>
       </c>
     </row>
     <row r="9">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B9" s="9">
-        <v>4865</v>
+        <v>5716.66</v>
       </c>
     </row>
     <row r="10">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <v>20400</v>
+        <v>218844</v>
       </c>
     </row>
     <row r="11">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <v>43265</v>
+        <v>273716.66</v>
       </c>
     </row>
     <row r="13">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B13" s="8">
-        <v>48130</v>
+        <v>279433.32</v>
       </c>
     </row>
     <row r="14">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <v>52995</v>
+        <v>285149.98</v>
       </c>
     </row>
     <row r="15">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <v>57860</v>
+        <v>290866.64</v>
       </c>
     </row>
     <row r="16">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B16" s="8">
-        <v>62725</v>
+        <v>296583.3</v>
       </c>
     </row>
     <row r="17">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B17" s="8">
-        <v>67590</v>
+        <v>302299.96</v>
       </c>
     </row>
     <row r="18">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <v>72455</v>
+        <v>308016.62</v>
       </c>
     </row>
     <row r="19">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <v>77320</v>
+        <v>313733.28</v>
       </c>
     </row>
     <row r="20">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B20" s="8">
-        <v>82185</v>
+        <v>319449.94</v>
       </c>
     </row>
     <row r="21">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B21" s="8">
-        <v>87050</v>
+        <v>325166.6</v>
       </c>
     </row>
     <row r="22">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B22" s="8">
-        <v>91915</v>
+        <v>330883.26</v>
       </c>
     </row>
     <row r="23">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="B23" s="8">
-        <v>96780</v>
+        <v>336599.92</v>
       </c>
     </row>
     <row r="24">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B24" s="8">
-        <v>101645</v>
+        <v>342316.58</v>
       </c>
     </row>
     <row r="25">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B25" s="11">
-        <v>5.6</v>
+        <v>3.67</v>
       </c>
     </row>
   </sheetData>
@@ -804,7 +804,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 to 2026-05-31</t>
+          <t>2026-05-01 to 2026-05-31</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>52300</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>-41180</v>
+        <v>-71900</v>
       </c>
     </row>
     <row r="8">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B8" s="9">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="9">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B11" s="13">
-        <v>14600</v>
+        <v>22700</v>
       </c>
     </row>
     <row r="12">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="B12" s="13">
-        <v>7845</v>
+        <v>14460</v>
       </c>
     </row>
     <row r="13">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="B13" s="13">
-        <v>49520</v>
+        <v>292500</v>
       </c>
     </row>
   </sheetData>
@@ -938,7 +938,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 to 2026-05-31</t>
+          <t>2026-05-01 to 2026-05-31</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>-41180</v>
+        <v>-71900</v>
       </c>
     </row>
     <row r="7">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="B4" s="8">
-        <v>38400</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="5">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <v>52300</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="6">
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>41180</v>
+        <v>71900</v>
       </c>
     </row>
     <row r="7">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="8">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>6800</v>
+        <v>72948</v>
       </c>
     </row>
     <row r="9">
@@ -1319,8 +1319,8 @@
           <t>runwayMonths</t>
         </is>
       </c>
-      <c r="B9" s="8">
-        <v>5.6</v>
+      <c r="B9" s="11">
+        <v>3.67</v>
       </c>
     </row>
     <row r="10">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <v>14600</v>
+        <v>22700</v>
       </c>
     </row>
     <row r="11">
@@ -1339,7 +1339,7 @@
           <t>revenueVsPriorPct</t>
         </is>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="10">
         <v>6.4</v>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="13">
@@ -1359,7 +1359,7 @@
           <t>profitVsPriorPct</t>
         </is>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="10">
         <v>3.1</v>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
           <t>coveragePct</t>
         </is>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="10">
         <v>94</v>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
           <t>transactionsCount</t>
         </is>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="12">
         <v>118</v>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
           <t>reserve_floor_months</t>
         </is>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="12">
         <v>3</v>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Detail</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
@@ -1429,12 +1429,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Not embedded</t>
+          <t>Transaction detail</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>The current frontend report snapshot does not include raw transaction rows. Server-side XLSX generation can populate this sheet from the transactions table.</t>
+          <t>This planning workbook summarizes your connected bank and card activity. Line-item transaction detail lives in your GoldFin Desk account and your own bank export.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/goldfin-template-vault.xlsx
+++ b/public/downloads/goldfin-template-vault.xlsx
@@ -220,7 +220,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Sample figures</t>
+          <t>Sample figures (pre-filled - type over them)</t>
         </is>
       </c>
     </row>
@@ -254,16 +254,36 @@
         <v>71900</v>
       </c>
     </row>
-    <row r="14"/>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Profit this month</t>
+        </is>
+      </c>
+      <c r="B14" s="8">
+        <v>24500</v>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Profit margin</t>
+        </is>
+      </c>
+      <c r="B15" s="10">
+        <v>25.41</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Prefer it filled from your bank every month? That is GoldFin Reports - goldfindesk.com/pricing</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>A planning artifact, not tax, accounting, credit, legal, or investment advice.</t>
         </is>
@@ -277,7 +297,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -353,62 +373,108 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>Owner pay you took (this month)</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
           <t>Reserve months target</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B11" s="15">
         <v>3</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Results</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Net cash</t>
-        </is>
-      </c>
-      <c r="B13" s="9">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Where you stand</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="str">
+        <f>IF(($B$8-$B$9)&lt;0,"You spent more than you earned this month - act now",IF($B$7&lt;$B$9*$B$11,"Below your cash reserve - build cash before new spending",IF($B$8=0,"No income yet - enter your numbers",IF(($B$8-$B$9)/$B$8&lt;0.1,"Thin profit margin - review pricing or costs","Healthy - profitable and above your reserve"))))</f>
+        <v>Healthy - profitable and above your reserve</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>The numbers that matter</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Profit this month (net cash)</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
         <f>$B$8-$B$9</f>
         <v>24500</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Cash coverage (months, if income paused)</t>
-        </is>
-      </c>
-      <c r="B14" s="11">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Profit margin</t>
+        </is>
+      </c>
+      <c r="B18" s="10">
+        <f>IF($B$8=0,0,($B$8-$B$9)/$B$8*100)</f>
+        <v>25.41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Owner pay as % of income</t>
+        </is>
+      </c>
+      <c r="B19" s="10">
+        <f>IF($B$8=0,0,$B$10/$B$8*100)</f>
+        <v>8.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Cash coverage (months at this burn)</t>
+        </is>
+      </c>
+      <c r="B20" s="11">
         <f>IF($B$9=0,0,$B$7/$B$9)</f>
         <v>3.73</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Reserve floor target</t>
         </is>
       </c>
-      <c r="B15" s="8">
-        <f>$B$9*$B$10</f>
+      <c r="B21" s="8">
+        <f>$B$9*$B$11</f>
         <v>215700</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Cash over / (under) reserve</t>
         </is>
       </c>
-      <c r="B16" s="9">
-        <f>$B$7-$B$9*$B$10</f>
+      <c r="B22" s="9">
+        <f>$B$7-$B$9*$B$11</f>
         <v>52300</v>
       </c>
     </row>
@@ -419,8 +485,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,190 +544,299 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Weekly money in</t>
+          <t>Cash floor to stay above</t>
         </is>
       </c>
       <c r="B8" s="14">
-        <v>22493</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Weekly money out</t>
-        </is>
-      </c>
-      <c r="B9" s="14">
-        <v>16777</v>
-      </c>
-    </row>
-    <row r="10"/>
+        <v>67000</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>13-week plan (edit any week's money in and out)</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Results</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Money in</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Money out</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Ending cash</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Weekly net cash</t>
-        </is>
-      </c>
-      <c r="B12" s="9">
-        <f>$B$8-$B$9</f>
-        <v>5716</v>
+          <t>Week 1</t>
+        </is>
+      </c>
+      <c r="B12" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C12" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D12" s="8">
+        <f>$B$7+B12-C12</f>
+        <v>273716</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>13-week cash path</t>
-        </is>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="B13" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C13" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D13" s="8">
+        <f>D12+B13-C13</f>
+        <v>279432</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 1</t>
-        </is>
-      </c>
-      <c r="B14" s="8">
-        <f>$B$7+($B$8-$B$9)*1</f>
-        <v>273716</v>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="B14" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C14" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D14" s="8">
+        <f>D13+B14-C14</f>
+        <v>285148</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 2</t>
-        </is>
-      </c>
-      <c r="B15" s="8">
-        <f>$B$7+($B$8-$B$9)*2</f>
-        <v>279432</v>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="B15" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C15" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D15" s="8">
+        <f>D14+B15-C15</f>
+        <v>290864</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 3</t>
-        </is>
-      </c>
-      <c r="B16" s="8">
-        <f>$B$7+($B$8-$B$9)*3</f>
-        <v>285148</v>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="B16" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C16" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D16" s="8">
+        <f>D15+B16-C16</f>
+        <v>296580</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 4</t>
-        </is>
-      </c>
-      <c r="B17" s="8">
-        <f>$B$7+($B$8-$B$9)*4</f>
-        <v>290864</v>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="B17" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C17" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D17" s="8">
+        <f>D16+B17-C17</f>
+        <v>302296</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 5</t>
-        </is>
-      </c>
-      <c r="B18" s="8">
-        <f>$B$7+($B$8-$B$9)*5</f>
-        <v>296580</v>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="B18" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C18" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D18" s="8">
+        <f>D17+B18-C18</f>
+        <v>308012</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 6</t>
-        </is>
-      </c>
-      <c r="B19" s="8">
-        <f>$B$7+($B$8-$B$9)*6</f>
-        <v>302296</v>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="B19" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C19" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D19" s="8">
+        <f>D18+B19-C19</f>
+        <v>313728</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 7</t>
-        </is>
-      </c>
-      <c r="B20" s="8">
-        <f>$B$7+($B$8-$B$9)*7</f>
-        <v>308012</v>
+          <t>Week 9</t>
+        </is>
+      </c>
+      <c r="B20" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C20" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D20" s="8">
+        <f>D19+B20-C20</f>
+        <v>319444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 8</t>
-        </is>
-      </c>
-      <c r="B21" s="8">
-        <f>$B$7+($B$8-$B$9)*8</f>
-        <v>313728</v>
+          <t>Week 10</t>
+        </is>
+      </c>
+      <c r="B21" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C21" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D21" s="8">
+        <f>D20+B21-C21</f>
+        <v>325160</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 9</t>
-        </is>
-      </c>
-      <c r="B22" s="8">
-        <f>$B$7+($B$8-$B$9)*9</f>
-        <v>319444</v>
+          <t>Week 11</t>
+        </is>
+      </c>
+      <c r="B22" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C22" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D22" s="8">
+        <f>D21+B22-C22</f>
+        <v>330876</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 10</t>
-        </is>
-      </c>
-      <c r="B23" s="8">
-        <f>$B$7+($B$8-$B$9)*10</f>
-        <v>325160</v>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="B23" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C23" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D23" s="8">
+        <f>D22+B23-C23</f>
+        <v>336592</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Projected cash - week 11</t>
-        </is>
-      </c>
-      <c r="B24" s="8">
-        <f>$B$7+($B$8-$B$9)*11</f>
-        <v>330876</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Projected cash - week 12</t>
-        </is>
-      </c>
-      <c r="B25" s="8">
-        <f>$B$7+($B$8-$B$9)*12</f>
-        <v>336592</v>
-      </c>
-    </row>
+          <t>Week 13</t>
+        </is>
+      </c>
+      <c r="B24" s="14">
+        <v>22493</v>
+      </c>
+      <c r="C24" s="14">
+        <v>16777</v>
+      </c>
+      <c r="D24" s="8">
+        <f>D23+B24-C24</f>
+        <v>342308</v>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Projected cash - week 13</t>
-        </is>
-      </c>
-      <c r="B26" s="8">
-        <f>$B$7+($B$8-$B$9)*13</f>
-        <v>342308</v>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Watch for the crunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Lowest weekly cash</t>
+        </is>
+      </c>
+      <c r="B27" s="8">
+        <f>MIN(D12:D24)</f>
+        <v>273716</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Weeks ending below your floor</t>
+        </is>
+      </c>
+      <c r="B28" s="12">
+        <f>COUNTIF(D12:D24,"&lt;"&amp;$B$8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="13" t="str">
+        <f>IF(MIN(D12:D24)&lt;0,"Cash goes negative in this window - line up funding or slow outflows",IF(MIN(D12:D24)&lt;$B$8,"Cash dips below your floor - watch the tightest week","Cash stays above your floor across all 13 weeks"))</f>
+        <v>Cash stays above your floor across all 13 weeks</v>
       </c>
     </row>
   </sheetData>
@@ -669,8 +846,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -709,14 +887,14 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Your inputs</t>
+          <t>Revenue &amp; assumptions</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Deposits (money in)</t>
+          <t>Revenue (deposits / money in)</t>
         </is>
       </c>
       <c r="B7" s="14">
@@ -726,62 +904,201 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Operating cash out</t>
-        </is>
-      </c>
-      <c r="B8" s="14">
-        <v>71900</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
           <t>Tax reserve rate (%)</t>
         </is>
       </c>
-      <c r="B9" s="16">
+      <c r="B8" s="16">
         <v>15</v>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Where the money went (edit these)</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Results</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>% of revenue</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Cash profit proxy</t>
-        </is>
-      </c>
-      <c r="B12" s="9">
-        <f>$B$7-$B$8</f>
-        <v>24500</v>
+          <t>Materials / cost of goods</t>
+        </is>
+      </c>
+      <c r="B12" s="14">
+        <v>15000</v>
+      </c>
+      <c r="C12" s="10">
+        <f>IF($B$7=0,0,B12/$B$7*100)</f>
+        <v>15.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Tax reserve target</t>
-        </is>
-      </c>
-      <c r="B13" s="8">
-        <f>$B$7*$B$9/100</f>
-        <v>14460</v>
+          <t>Payroll &amp; contractors</t>
+        </is>
+      </c>
+      <c r="B13" s="14">
+        <v>30000</v>
+      </c>
+      <c r="C13" s="10">
+        <f>IF($B$7=0,0,B13/$B$7*100)</f>
+        <v>31.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>After-tax cash proxy</t>
-        </is>
-      </c>
-      <c r="B14" s="9">
-        <f>($B$7-$B$8)-$B$7*$B$9/100</f>
-        <v>10040</v>
+          <t>Rent &amp; utilities</t>
+        </is>
+      </c>
+      <c r="B14" s="14">
+        <v>6000</v>
+      </c>
+      <c r="C14" s="10">
+        <f>IF($B$7=0,0,B14/$B$7*100)</f>
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Software &amp; subscriptions</t>
+        </is>
+      </c>
+      <c r="B15" s="14">
+        <v>4500</v>
+      </c>
+      <c r="C15" s="10">
+        <f>IF($B$7=0,0,B15/$B$7*100)</f>
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Marketing &amp; sales</t>
+        </is>
+      </c>
+      <c r="B16" s="14">
+        <v>5400</v>
+      </c>
+      <c r="C16" s="10">
+        <f>IF($B$7=0,0,B16/$B$7*100)</f>
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Owner pay</t>
+        </is>
+      </c>
+      <c r="B17" s="14">
+        <v>8000</v>
+      </c>
+      <c r="C17" s="10">
+        <f>IF($B$7=0,0,B17/$B$7*100)</f>
+        <v>8.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B18" s="14">
+        <v>3000</v>
+      </c>
+      <c r="C18" s="10">
+        <f>IF($B$7=0,0,B18/$B$7*100)</f>
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Total spending</t>
+        </is>
+      </c>
+      <c r="B19" s="9">
+        <f>SUM(B12:B18)</f>
+        <v>71900</v>
+      </c>
+      <c r="C19" s="10">
+        <f>IF($B$7=0,0,B19/$B$7*100)</f>
+        <v>74.59</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Operating profit</t>
+        </is>
+      </c>
+      <c r="B22" s="9">
+        <f>$B$7-B19</f>
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Profit margin</t>
+        </is>
+      </c>
+      <c r="B23" s="10">
+        <f>IF($B$7=0,0,($B$7-B19)/$B$7*100)</f>
+        <v>25.41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Tax reserve target</t>
+        </is>
+      </c>
+      <c r="B24" s="8">
+        <f>($B$7-B19)*$B$8/100</f>
+        <v>3675</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Cash left after tax reserve</t>
+        </is>
+      </c>
+      <c r="B25" s="9">
+        <f>($B$7-B19)-($B$7-B19)*$B$8/100</f>
+        <v>20825</v>
       </c>
     </row>
   </sheetData>
@@ -791,8 +1108,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -823,7 +1143,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>List your recurring vendors and their monthly cost in the shaded cells. Totals update automatically; add rows as needed.</t>
+          <t>List each recurring vendor, its monthly cost, and whether to Keep, Review, or Cut it. Totals and savings update as you edit.</t>
         </is>
       </c>
     </row>
@@ -831,7 +1151,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Recurring vendors</t>
+          <t>Recurring vendors (edit these)</t>
         </is>
       </c>
     </row>
@@ -843,7 +1163,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Monthly cost</t>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>% of total</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Keep / Review / Cut</t>
         </is>
       </c>
     </row>
@@ -856,6 +1191,19 @@
       <c r="B8" s="14">
         <v>49</v>
       </c>
+      <c r="C8" s="8">
+        <f>B8*12</f>
+        <v>588</v>
+      </c>
+      <c r="D8" s="10">
+        <f>IF($B$14=0,0,B8/$B$14*100)</f>
+        <v>10.02</v>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
@@ -866,6 +1214,19 @@
       <c r="B9" s="14">
         <v>30</v>
       </c>
+      <c r="C9" s="8">
+        <f>B9*12</f>
+        <v>360</v>
+      </c>
+      <c r="D9" s="10">
+        <f>IF($B$14=0,0,B9/$B$14*100)</f>
+        <v>6.13</v>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Cut</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
@@ -876,6 +1237,19 @@
       <c r="B10" s="14">
         <v>410</v>
       </c>
+      <c r="C10" s="8">
+        <f>B10*12</f>
+        <v>4920</v>
+      </c>
+      <c r="D10" s="10">
+        <f>IF($B$14=0,0,B10/$B$14*100)</f>
+        <v>83.84</v>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -886,6 +1260,19 @@
       <c r="B11" s="14">
         <v>0</v>
       </c>
+      <c r="C11" s="8">
+        <f>B11*12</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="10">
+        <f>IF($B$14=0,0,B11/$B$14*100)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
@@ -896,6 +1283,19 @@
       <c r="B12" s="14">
         <v>0</v>
       </c>
+      <c r="C12" s="8">
+        <f>B12*12</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="10">
+        <f>IF($B$14=0,0,B12/$B$14*100)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -906,35 +1306,70 @@
       <c r="B13" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Totals</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Total monthly recurring</t>
-        </is>
-      </c>
-      <c r="B16" s="9">
+      <c r="C13" s="8">
+        <f>B13*12</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="10">
+        <f>IF($B$14=0,0,B13/$B$14*100)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
         <f>SUM(B8:B13)</f>
         <v>489</v>
       </c>
+      <c r="C14" s="8">
+        <f>SUM(C8:C13)</f>
+        <v>5868</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Your savings opportunity</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Annualized</t>
+          <t>Monthly cost of vendors marked Cut</t>
         </is>
       </c>
       <c r="B17" s="8">
-        <f>SUM(B8:B13)*12</f>
-        <v>5868</v>
+        <f>SUMIF(E8:E13,"Cut",B8:B13)</f>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Annual savings if you cut them</t>
+        </is>
+      </c>
+      <c r="B18" s="8">
+        <f>SUMIF(E8:E13,"Cut",C8:C13)</f>
+        <v>948</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="13" t="str">
+        <f>IF(SUMIF(E8:E13,"Cut",C8:C13)&gt;0,"Cutting the vendors you marked Cut saves the annual amount above","Mark any vendor Cut to see the annual savings")</f>
+        <v>Cutting the vendors you marked Cut saves the annual amount above</v>
       </c>
     </row>
   </sheetData>
